--- a/data/nzd0032/nzd0032.xlsx
+++ b/data/nzd0032/nzd0032.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F541"/>
+  <dimension ref="A1:F542"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13402,6 +13402,30 @@
         <v>317.48</v>
       </c>
       <c r="F541" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-20 22:17:54+00:00</t>
+        </is>
+      </c>
+      <c r="B542" t="n">
+        <v>391.27</v>
+      </c>
+      <c r="C542" t="n">
+        <v>344.71</v>
+      </c>
+      <c r="D542" t="n">
+        <v>328.98</v>
+      </c>
+      <c r="E542" t="n">
+        <v>316.94</v>
+      </c>
+      <c r="F542" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -13418,7 +13442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B594"/>
+  <dimension ref="A1:B595"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19361,6 +19385,16 @@
       </c>
       <c r="B594" t="n">
         <v>-0.48</v>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>2025-11-20 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B595" t="n">
+        <v>0.42</v>
       </c>
     </row>
   </sheetData>
@@ -19529,28 +19563,28 @@
         <v>0.0793</v>
       </c>
       <c r="I2" t="n">
-        <v>3.160851768478382</v>
+        <v>3.147685182285378</v>
       </c>
       <c r="J2" t="n">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="K2" t="n">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="L2" t="n">
-        <v>0.218000629240714</v>
+        <v>0.217051525370499</v>
       </c>
       <c r="M2" t="n">
-        <v>35.72418251983287</v>
+        <v>35.72073393112018</v>
       </c>
       <c r="N2" t="n">
-        <v>2094.312439953625</v>
+        <v>2092.924218001531</v>
       </c>
       <c r="O2" t="n">
-        <v>45.76365850709081</v>
+        <v>45.74848869636603</v>
       </c>
       <c r="P2" t="n">
-        <v>344.9687999756461</v>
+        <v>345.0995549465701</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -19607,28 +19641,28 @@
         <v>0.0712</v>
       </c>
       <c r="I3" t="n">
-        <v>0.336825383769167</v>
+        <v>0.3327840143388231</v>
       </c>
       <c r="J3" t="n">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="K3" t="n">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1392849764378724</v>
+        <v>0.136199335121959</v>
       </c>
       <c r="M3" t="n">
-        <v>5.041797935545592</v>
+        <v>5.059516944182135</v>
       </c>
       <c r="N3" t="n">
-        <v>40.68819425485476</v>
+        <v>40.85048502544851</v>
       </c>
       <c r="O3" t="n">
-        <v>6.378729830840522</v>
+        <v>6.391438415994362</v>
       </c>
       <c r="P3" t="n">
-        <v>347.2121070759425</v>
+        <v>347.2522749054096</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -19685,28 +19719,28 @@
         <v>0.079</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3277814066429519</v>
+        <v>0.3224995909491103</v>
       </c>
       <c r="J4" t="n">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="K4" t="n">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="L4" t="n">
-        <v>0.07374227929145638</v>
+        <v>0.07147495236223123</v>
       </c>
       <c r="M4" t="n">
-        <v>7.220776270276128</v>
+        <v>7.238320868968749</v>
       </c>
       <c r="N4" t="n">
-        <v>78.32268991809836</v>
+        <v>78.58358609950648</v>
       </c>
       <c r="O4" t="n">
-        <v>8.850010729829561</v>
+        <v>8.864738354825057</v>
       </c>
       <c r="P4" t="n">
-        <v>335.2136565478922</v>
+        <v>335.2661533749516</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -19763,28 +19797,28 @@
         <v>0.0843</v>
       </c>
       <c r="I5" t="n">
-        <v>0.341850006737754</v>
+        <v>0.3353785722179158</v>
       </c>
       <c r="J5" t="n">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="K5" t="n">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="L5" t="n">
-        <v>0.06224466111278659</v>
+        <v>0.05993986307037591</v>
       </c>
       <c r="M5" t="n">
-        <v>8.303964980564393</v>
+        <v>8.321201634148661</v>
       </c>
       <c r="N5" t="n">
-        <v>102.1791546649942</v>
+        <v>102.5992702281762</v>
       </c>
       <c r="O5" t="n">
-        <v>10.10837052471832</v>
+        <v>10.12912978632302</v>
       </c>
       <c r="P5" t="n">
-        <v>326.1418329662866</v>
+        <v>326.2061536087523</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -19822,7 +19856,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F541"/>
+  <dimension ref="A1:F542"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37105,6 +37139,38 @@
         </is>
       </c>
     </row>
+    <row r="542">
+      <c r="A542" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-20 22:17:54+00:00</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>-34.93971790097073,173.57369984992533</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>-34.94025375002869,173.5728667207881</t>
+        </is>
+      </c>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>-34.94103642051837,173.57263960239536</t>
+        </is>
+      </c>
+      <c r="E542" t="inlineStr">
+        <is>
+          <t>-34.941806612602626,173.57261118018226</t>
+        </is>
+      </c>
+      <c r="F542" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0032/nzd0032.xlsx
+++ b/data/nzd0032/nzd0032.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F542"/>
+  <dimension ref="A1:F544"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13428,6 +13428,54 @@
       <c r="F542" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-06 22:17:51+00:00</t>
+        </is>
+      </c>
+      <c r="B543" t="n">
+        <v>398.62</v>
+      </c>
+      <c r="C543" t="n">
+        <v>343.7</v>
+      </c>
+      <c r="D543" t="n">
+        <v>328.75</v>
+      </c>
+      <c r="E543" t="n">
+        <v>317.01</v>
+      </c>
+      <c r="F543" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-14 22:17:57+00:00</t>
+        </is>
+      </c>
+      <c r="B544" t="n">
+        <v>401.3</v>
+      </c>
+      <c r="C544" t="n">
+        <v>343.13</v>
+      </c>
+      <c r="D544" t="n">
+        <v>328.24</v>
+      </c>
+      <c r="E544" t="n">
+        <v>316.5</v>
+      </c>
+      <c r="F544" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -13442,7 +13490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B595"/>
+  <dimension ref="A1:B597"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19395,6 +19443,26 @@
       </c>
       <c r="B595" t="n">
         <v>0.42</v>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>2025-12-06 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B596" t="n">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>2025-12-14 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B597" t="n">
+        <v>-0.49</v>
       </c>
     </row>
   </sheetData>
@@ -19563,28 +19631,28 @@
         <v>0.0793</v>
       </c>
       <c r="I2" t="n">
-        <v>3.147685182285378</v>
+        <v>3.127720617368671</v>
       </c>
       <c r="J2" t="n">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K2" t="n">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="L2" t="n">
-        <v>0.217051525370499</v>
+        <v>0.2160040913778022</v>
       </c>
       <c r="M2" t="n">
-        <v>35.72073393112018</v>
+        <v>35.68348273244544</v>
       </c>
       <c r="N2" t="n">
-        <v>2092.924218001531</v>
+        <v>2088.039758920864</v>
       </c>
       <c r="O2" t="n">
-        <v>45.74848869636603</v>
+        <v>45.69507368328521</v>
       </c>
       <c r="P2" t="n">
-        <v>345.0995549465701</v>
+        <v>345.2983284957503</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -19641,28 +19709,28 @@
         <v>0.0712</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3327840143388231</v>
+        <v>0.3238747253914859</v>
       </c>
       <c r="J3" t="n">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K3" t="n">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="L3" t="n">
-        <v>0.136199335121959</v>
+        <v>0.1292427691966003</v>
       </c>
       <c r="M3" t="n">
-        <v>5.059516944182135</v>
+        <v>5.100063517262917</v>
       </c>
       <c r="N3" t="n">
-        <v>40.85048502544851</v>
+        <v>41.27976621097241</v>
       </c>
       <c r="O3" t="n">
-        <v>6.391438415994362</v>
+        <v>6.424933167821469</v>
       </c>
       <c r="P3" t="n">
-        <v>347.2522749054096</v>
+        <v>347.3410525047901</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -19719,28 +19787,28 @@
         <v>0.079</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3224995909491103</v>
+        <v>0.3117108576526045</v>
       </c>
       <c r="J4" t="n">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K4" t="n">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="L4" t="n">
-        <v>0.07147495236223123</v>
+        <v>0.06691146631325107</v>
       </c>
       <c r="M4" t="n">
-        <v>7.238320868968749</v>
+        <v>7.274271365470371</v>
       </c>
       <c r="N4" t="n">
-        <v>78.58358609950648</v>
+        <v>79.14408167503289</v>
       </c>
       <c r="O4" t="n">
-        <v>8.864738354825057</v>
+        <v>8.896295952531755</v>
       </c>
       <c r="P4" t="n">
-        <v>335.2661533749516</v>
+        <v>335.3736585680705</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -19797,28 +19865,28 @@
         <v>0.0843</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3353785722179158</v>
+        <v>0.3224584031961744</v>
       </c>
       <c r="J5" t="n">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="K5" t="n">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="L5" t="n">
-        <v>0.05993986307037591</v>
+        <v>0.05545888859706649</v>
       </c>
       <c r="M5" t="n">
-        <v>8.321201634148661</v>
+        <v>8.35580110052247</v>
       </c>
       <c r="N5" t="n">
-        <v>102.5992702281762</v>
+        <v>103.4402068216976</v>
       </c>
       <c r="O5" t="n">
-        <v>10.12912978632302</v>
+        <v>10.17055587574728</v>
       </c>
       <c r="P5" t="n">
-        <v>326.2061536087523</v>
+        <v>326.3348974682415</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -19856,7 +19924,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F542"/>
+  <dimension ref="A1:F544"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37171,6 +37239,70 @@
         </is>
       </c>
     </row>
+    <row r="543">
+      <c r="A543" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-06 22:17:51+00:00</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>-34.939743774515115,173.57377394830704</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>-34.94025171530619,173.57285594045646</t>
+        </is>
+      </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>-34.94103648772852,173.57263708510632</t>
+        </is>
+      </c>
+      <c r="E543" t="inlineStr">
+        <is>
+          <t>-34.94180653991365,173.57261194162376</t>
+        </is>
+      </c>
+      <c r="F543" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-14 22:17:57+00:00</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>-34.93975320866685,173.57380096650394</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>-34.94025056699704,173.57284985650713</t>
+        </is>
+      </c>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>-34.941036636759534,173.57263150329146</t>
+        </is>
+      </c>
+      <c r="E544" t="inlineStr">
+        <is>
+          <t>-34.94180706950466,173.57260639397862</t>
+        </is>
+      </c>
+      <c r="F544" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0032/nzd0032.xlsx
+++ b/data/nzd0032/nzd0032.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F544"/>
+  <dimension ref="A1:F547"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13474,6 +13474,78 @@
         <v>316.5</v>
       </c>
       <c r="F544" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-30 22:18:00+00:00</t>
+        </is>
+      </c>
+      <c r="B545" t="n">
+        <v>409.53</v>
+      </c>
+      <c r="C545" t="n">
+        <v>339.43</v>
+      </c>
+      <c r="D545" t="n">
+        <v>324.94</v>
+      </c>
+      <c r="E545" t="n">
+        <v>314.99</v>
+      </c>
+      <c r="F545" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:11:42+00:00</t>
+        </is>
+      </c>
+      <c r="B546" t="n">
+        <v>416.58</v>
+      </c>
+      <c r="C546" t="n">
+        <v>340.09</v>
+      </c>
+      <c r="D546" t="n">
+        <v>325.84</v>
+      </c>
+      <c r="E546" t="n">
+        <v>316.12</v>
+      </c>
+      <c r="F546" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-24 22:11:43+00:00</t>
+        </is>
+      </c>
+      <c r="B547" t="n">
+        <v>431.68</v>
+      </c>
+      <c r="C547" t="n">
+        <v>339.54</v>
+      </c>
+      <c r="D547" t="n">
+        <v>326.68</v>
+      </c>
+      <c r="E547" t="n">
+        <v>316.69</v>
+      </c>
+      <c r="F547" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -13490,7 +13562,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B597"/>
+  <dimension ref="A1:B600"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19463,6 +19535,36 @@
       </c>
       <c r="B597" t="n">
         <v>-0.49</v>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>2025-12-30 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B598" t="n">
+        <v>-0.64</v>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B599" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>2026-01-24 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B600" t="n">
+        <v>0.55</v>
       </c>
     </row>
   </sheetData>
@@ -19631,28 +19733,28 @@
         <v>0.0793</v>
       </c>
       <c r="I2" t="n">
-        <v>3.127720617368671</v>
+        <v>3.118473881200988</v>
       </c>
       <c r="J2" t="n">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="K2" t="n">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2160040913778022</v>
+        <v>0.2169441089870005</v>
       </c>
       <c r="M2" t="n">
-        <v>35.68348273244544</v>
+        <v>35.54250265836743</v>
       </c>
       <c r="N2" t="n">
-        <v>2088.039758920864</v>
+        <v>2077.288780954759</v>
       </c>
       <c r="O2" t="n">
-        <v>45.69507368328521</v>
+        <v>45.57728360658145</v>
       </c>
       <c r="P2" t="n">
-        <v>345.2983284957503</v>
+        <v>345.3906375053767</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -19709,28 +19811,28 @@
         <v>0.0712</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3238747253914859</v>
+        <v>0.3068572244351608</v>
       </c>
       <c r="J3" t="n">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="K3" t="n">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1292427691966003</v>
+        <v>0.1152956585446774</v>
       </c>
       <c r="M3" t="n">
-        <v>5.100063517262917</v>
+        <v>5.184735999665524</v>
       </c>
       <c r="N3" t="n">
-        <v>41.27976621097241</v>
+        <v>42.47456373167715</v>
       </c>
       <c r="O3" t="n">
-        <v>6.424933167821469</v>
+        <v>6.517251240490668</v>
       </c>
       <c r="P3" t="n">
-        <v>347.3410525047901</v>
+        <v>347.5112981275524</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -19787,28 +19889,28 @@
         <v>0.079</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3117108576526045</v>
+        <v>0.2930376016591743</v>
       </c>
       <c r="J4" t="n">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="K4" t="n">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="L4" t="n">
-        <v>0.06691146631325107</v>
+        <v>0.05906046087016359</v>
       </c>
       <c r="M4" t="n">
-        <v>7.274271365470371</v>
+        <v>7.34205599754189</v>
       </c>
       <c r="N4" t="n">
-        <v>79.14408167503289</v>
+        <v>80.4234328452094</v>
       </c>
       <c r="O4" t="n">
-        <v>8.896295952531755</v>
+        <v>8.96791128664916</v>
       </c>
       <c r="P4" t="n">
-        <v>335.3736585680705</v>
+        <v>335.5604588817972</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -19865,28 +19967,28 @@
         <v>0.0843</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3224584031961744</v>
+        <v>0.3025985342598818</v>
       </c>
       <c r="J5" t="n">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="K5" t="n">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="L5" t="n">
-        <v>0.05545888859706649</v>
+        <v>0.04884836841269546</v>
       </c>
       <c r="M5" t="n">
-        <v>8.35580110052247</v>
+        <v>8.410810142918743</v>
       </c>
       <c r="N5" t="n">
-        <v>103.4402068216976</v>
+        <v>104.8103937529004</v>
       </c>
       <c r="O5" t="n">
-        <v>10.17055587574728</v>
+        <v>10.23769474798406</v>
       </c>
       <c r="P5" t="n">
-        <v>326.3348974682415</v>
+        <v>326.5335693737305</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -19924,7 +20026,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F544"/>
+  <dimension ref="A1:F547"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37303,6 +37405,102 @@
         </is>
       </c>
     </row>
+    <row r="545">
+      <c r="A545" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-30 22:18:00+00:00</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>-34.93978217992317,173.573883936602</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>-34.940243113052944,173.57281036420852</t>
+        </is>
+      </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>-34.941037601071564,173.57259538566547</t>
+        </is>
+      </c>
+      <c r="E545" t="inlineStr">
+        <is>
+          <t>-34.94180863750796,173.57258996859744</t>
+        </is>
+      </c>
+      <c r="F545" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:11:42+00:00</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>-34.939806997296365,173.5739550106687</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>-34.940244442676345,173.57281740878022</t>
+        </is>
+      </c>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>-34.94103733807843,173.5726052359272</t>
+        </is>
+      </c>
+      <c r="E546" t="inlineStr">
+        <is>
+          <t>-34.941807464101714,173.57260226043903</t>
+        </is>
+      </c>
+      <c r="F546" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-24 22:11:43+00:00</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>-34.93986015209589,173.57410724037246</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>-34.94024333465688,173.5728115383038</t>
+        </is>
+      </c>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>-34.94103709261746,173.57261442950474</t>
+        </is>
+      </c>
+      <c r="E547" t="inlineStr">
+        <is>
+          <t>-34.94180687220607,173.57260846074837</t>
+        </is>
+      </c>
+      <c r="F547" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0032/nzd0032.xlsx
+++ b/data/nzd0032/nzd0032.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F547"/>
+  <dimension ref="A1:F548"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13548,6 +13548,30 @@
       <c r="F547" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-24 22:17:36+00:00</t>
+        </is>
+      </c>
+      <c r="B548" t="n">
+        <v>461.42</v>
+      </c>
+      <c r="C548" t="n">
+        <v>342.87</v>
+      </c>
+      <c r="D548" t="n">
+        <v>329.23</v>
+      </c>
+      <c r="E548" t="n">
+        <v>321.14</v>
+      </c>
+      <c r="F548" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -13562,7 +13586,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B600"/>
+  <dimension ref="A1:B601"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19565,6 +19589,16 @@
       </c>
       <c r="B600" t="n">
         <v>0.55</v>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>2026-02-24 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B601" t="n">
+        <v>0.04</v>
       </c>
     </row>
   </sheetData>
@@ -19733,28 +19767,28 @@
         <v>0.0793</v>
       </c>
       <c r="I2" t="n">
-        <v>3.118473881200988</v>
+        <v>3.130151643832131</v>
       </c>
       <c r="J2" t="n">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="K2" t="n">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2169441089870005</v>
+        <v>0.218731446194682</v>
       </c>
       <c r="M2" t="n">
-        <v>35.54250265836743</v>
+        <v>35.54255844097082</v>
       </c>
       <c r="N2" t="n">
-        <v>2077.288780954759</v>
+        <v>2075.457791222209</v>
       </c>
       <c r="O2" t="n">
-        <v>45.57728360658145</v>
+        <v>45.55719253007377</v>
       </c>
       <c r="P2" t="n">
-        <v>345.3906375053767</v>
+        <v>345.2732267037621</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -19811,28 +19845,28 @@
         <v>0.0712</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3068572244351608</v>
+        <v>0.3023599567001091</v>
       </c>
       <c r="J3" t="n">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="K3" t="n">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1152956585446774</v>
+        <v>0.1120187353583357</v>
       </c>
       <c r="M3" t="n">
-        <v>5.184735999665524</v>
+        <v>5.205203177470606</v>
       </c>
       <c r="N3" t="n">
-        <v>42.47456373167715</v>
+        <v>42.69459621032983</v>
       </c>
       <c r="O3" t="n">
-        <v>6.517251240490668</v>
+        <v>6.534110208003063</v>
       </c>
       <c r="P3" t="n">
-        <v>347.5112981275524</v>
+        <v>347.5565433569157</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -19889,28 +19923,28 @@
         <v>0.079</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2930376016591743</v>
+        <v>0.2880739894504145</v>
       </c>
       <c r="J4" t="n">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="K4" t="n">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="L4" t="n">
-        <v>0.05906046087016359</v>
+        <v>0.05716245987502377</v>
       </c>
       <c r="M4" t="n">
-        <v>7.34205599754189</v>
+        <v>7.357434911887348</v>
       </c>
       <c r="N4" t="n">
-        <v>80.4234328452094</v>
+        <v>80.63902625787438</v>
       </c>
       <c r="O4" t="n">
-        <v>8.96791128664916</v>
+        <v>8.979923510691746</v>
       </c>
       <c r="P4" t="n">
-        <v>335.5604588817972</v>
+        <v>335.6103958181964</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -19967,28 +20001,28 @@
         <v>0.0843</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3025985342598818</v>
+        <v>0.2978755288473198</v>
       </c>
       <c r="J5" t="n">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="K5" t="n">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="L5" t="n">
-        <v>0.04884836841269546</v>
+        <v>0.04744604497039384</v>
       </c>
       <c r="M5" t="n">
-        <v>8.410810142918743</v>
+        <v>8.419542829093608</v>
       </c>
       <c r="N5" t="n">
-        <v>104.8103937529004</v>
+        <v>104.9471007585152</v>
       </c>
       <c r="O5" t="n">
-        <v>10.23769474798406</v>
+        <v>10.2443692220905</v>
       </c>
       <c r="P5" t="n">
-        <v>326.5335693737305</v>
+        <v>326.581085660455</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -20026,7 +20060,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F547"/>
+  <dimension ref="A1:F548"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37501,6 +37535,38 @@
         </is>
       </c>
     </row>
+    <row r="548">
+      <c r="A548" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-24 22:17:36+00:00</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>-34.939964841844855,173.57440706288673</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>-34.940250043206795,173.5728470813724</t>
+        </is>
+      </c>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>-34.94103634746383,173.57264233857907</t>
+        </is>
+      </c>
+      <c r="E548" t="inlineStr">
+        <is>
+          <t>-34.9418022512555,173.57265686666898</t>
+        </is>
+      </c>
+      <c r="F548" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0032/nzd0032.xlsx
+++ b/data/nzd0032/nzd0032.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F548"/>
+  <dimension ref="A1:F551"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13572,6 +13572,78 @@
       <c r="F548" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-28 22:17:16+00:00</t>
+        </is>
+      </c>
+      <c r="B549" t="n">
+        <v>475.57</v>
+      </c>
+      <c r="C549" t="n">
+        <v>345.67</v>
+      </c>
+      <c r="D549" t="n">
+        <v>330.79</v>
+      </c>
+      <c r="E549" t="n">
+        <v>322.55</v>
+      </c>
+      <c r="F549" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:11:19+00:00</t>
+        </is>
+      </c>
+      <c r="B550" t="n">
+        <v>464.19</v>
+      </c>
+      <c r="C550" t="n">
+        <v>346.3</v>
+      </c>
+      <c r="D550" t="n">
+        <v>331.14</v>
+      </c>
+      <c r="E550" t="n">
+        <v>322.92</v>
+      </c>
+      <c r="F550" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:17:21+00:00</t>
+        </is>
+      </c>
+      <c r="B551" t="n">
+        <v>456.93</v>
+      </c>
+      <c r="C551" t="n">
+        <v>348.19</v>
+      </c>
+      <c r="D551" t="n">
+        <v>332.5</v>
+      </c>
+      <c r="E551" t="n">
+        <v>323.51</v>
+      </c>
+      <c r="F551" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -13586,7 +13658,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B601"/>
+  <dimension ref="A1:B604"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19599,6 +19671,36 @@
       </c>
       <c r="B601" t="n">
         <v>0.04</v>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>2026-03-28 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B602" t="n">
+        <v>-0.59</v>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B603" t="n">
+        <v>-0.48</v>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B604" t="n">
+        <v>0.8</v>
       </c>
     </row>
   </sheetData>
@@ -19767,28 +19869,28 @@
         <v>0.0793</v>
       </c>
       <c r="I2" t="n">
-        <v>3.130151643832131</v>
+        <v>3.168678016905996</v>
       </c>
       <c r="J2" t="n">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="K2" t="n">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="L2" t="n">
-        <v>0.218731446194682</v>
+        <v>0.2243842446944535</v>
       </c>
       <c r="M2" t="n">
-        <v>35.54255844097082</v>
+        <v>35.56171545410756</v>
       </c>
       <c r="N2" t="n">
-        <v>2075.457791222209</v>
+        <v>2071.636655635795</v>
       </c>
       <c r="O2" t="n">
-        <v>45.55719253007377</v>
+        <v>45.51523542327113</v>
       </c>
       <c r="P2" t="n">
-        <v>345.2732267037621</v>
+        <v>344.8840018811654</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -19845,28 +19947,28 @@
         <v>0.0712</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3023599567001091</v>
+        <v>0.2930425560458905</v>
       </c>
       <c r="J3" t="n">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="K3" t="n">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1120187353583357</v>
+        <v>0.106123270054326</v>
       </c>
       <c r="M3" t="n">
-        <v>5.205203177470606</v>
+        <v>5.238176727258246</v>
       </c>
       <c r="N3" t="n">
-        <v>42.69459621032983</v>
+        <v>42.89338208568804</v>
       </c>
       <c r="O3" t="n">
-        <v>6.534110208003063</v>
+        <v>6.54930393902192</v>
       </c>
       <c r="P3" t="n">
-        <v>347.5565433569157</v>
+        <v>347.6507350186717</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -19923,28 +20025,28 @@
         <v>0.079</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2880739894504145</v>
+        <v>0.2757088265986481</v>
       </c>
       <c r="J4" t="n">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="K4" t="n">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="L4" t="n">
-        <v>0.05716245987502377</v>
+        <v>0.0527478988100577</v>
       </c>
       <c r="M4" t="n">
-        <v>7.357434911887348</v>
+        <v>7.388224278480021</v>
       </c>
       <c r="N4" t="n">
-        <v>80.63902625787438</v>
+        <v>80.95126664009864</v>
       </c>
       <c r="O4" t="n">
-        <v>8.979923510691746</v>
+        <v>8.997292183768327</v>
       </c>
       <c r="P4" t="n">
-        <v>335.6103958181964</v>
+        <v>335.7354075980586</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -20001,28 +20103,28 @@
         <v>0.0843</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2978755288473198</v>
+        <v>0.2858022085783356</v>
       </c>
       <c r="J5" t="n">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="K5" t="n">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="L5" t="n">
-        <v>0.04744604497039384</v>
+        <v>0.04406187736311462</v>
       </c>
       <c r="M5" t="n">
-        <v>8.419542829093608</v>
+        <v>8.434921071649805</v>
       </c>
       <c r="N5" t="n">
-        <v>104.9471007585152</v>
+        <v>105.0896246845879</v>
       </c>
       <c r="O5" t="n">
-        <v>10.2443692220905</v>
+        <v>10.25132306995482</v>
       </c>
       <c r="P5" t="n">
-        <v>326.581085660455</v>
+        <v>326.7031518414523</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -20060,7 +20162,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F548"/>
+  <dimension ref="A1:F551"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37567,6 +37669,102 @@
         </is>
       </c>
     </row>
+    <row r="549">
+      <c r="A549" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-28 22:17:16+00:00</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>-34.94001465193651,173.57454971575973</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>-34.940255684021444,173.57287696744046</t>
+        </is>
+      </c>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>-34.94103589160196,173.57265941236545</t>
+        </is>
+      </c>
+      <c r="E549" t="inlineStr">
+        <is>
+          <t>-34.94180078708514,173.57267220427408</t>
+        </is>
+      </c>
+      <c r="F549" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:11:19+00:00</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>-34.93997459266767,173.57443498855937</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>-34.940256953203715,173.57288369180637</t>
+        </is>
+      </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>-34.941035789324935,173.57266324302262</t>
+        </is>
+      </c>
+      <c r="E550" t="inlineStr">
+        <is>
+          <t>-34.941800402869895,173.5726762290356</t>
+        </is>
+      </c>
+      <c r="F550" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:17:21+00:00</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>-34.9399490363457,173.57436179709907</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>-34.94026076074831,173.5729038649052</t>
+        </is>
+      </c>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>-34.94103539190447,173.5726781278618</t>
+        </is>
+      </c>
+      <c r="E551" t="inlineStr">
+        <is>
+          <t>-34.941799790202076,173.5726826468985</t>
+        </is>
+      </c>
+      <c r="F551" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0032/nzd0032.xlsx
+++ b/data/nzd0032/nzd0032.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F551"/>
+  <dimension ref="A1:F555"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13642,6 +13642,102 @@
         <v>323.51</v>
       </c>
       <c r="F551" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:17:05+00:00</t>
+        </is>
+      </c>
+      <c r="B552" t="n">
+        <v>445.59</v>
+      </c>
+      <c r="C552" t="n">
+        <v>347.92</v>
+      </c>
+      <c r="D552" t="n">
+        <v>331.82</v>
+      </c>
+      <c r="E552" t="n">
+        <v>322.47</v>
+      </c>
+      <c r="F552" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:11:06+00:00</t>
+        </is>
+      </c>
+      <c r="B553" t="n">
+        <v>436.79</v>
+      </c>
+      <c r="C553" t="n">
+        <v>347.22</v>
+      </c>
+      <c r="D553" t="n">
+        <v>331.27</v>
+      </c>
+      <c r="E553" t="n">
+        <v>321.38</v>
+      </c>
+      <c r="F553" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:10:40+00:00</t>
+        </is>
+      </c>
+      <c r="B554" t="n">
+        <v>414.5</v>
+      </c>
+      <c r="C554" t="n">
+        <v>347.66</v>
+      </c>
+      <c r="D554" t="n">
+        <v>331.98</v>
+      </c>
+      <c r="E554" t="n">
+        <v>321.71</v>
+      </c>
+      <c r="F554" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:49+00:00</t>
+        </is>
+      </c>
+      <c r="B555" t="n">
+        <v>400.69</v>
+      </c>
+      <c r="C555" t="n">
+        <v>347.63</v>
+      </c>
+      <c r="D555" t="n">
+        <v>331.88</v>
+      </c>
+      <c r="E555" t="n">
+        <v>321.16</v>
+      </c>
+      <c r="F555" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -13658,7 +13754,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B604"/>
+  <dimension ref="A1:B608"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19701,6 +19797,46 @@
       </c>
       <c r="B604" t="n">
         <v>0.8</v>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B605" t="n">
+        <v>-0.33</v>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B606" t="n">
+        <v>-0.01</v>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B607" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B608" t="n">
+        <v>0.09</v>
       </c>
     </row>
   </sheetData>
@@ -19869,28 +20005,28 @@
         <v>0.0793</v>
       </c>
       <c r="I2" t="n">
-        <v>3.168678016905996</v>
+        <v>3.161265540541654</v>
       </c>
       <c r="J2" t="n">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="K2" t="n">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2243842446944535</v>
+        <v>0.2261146599477705</v>
       </c>
       <c r="M2" t="n">
-        <v>35.56171545410756</v>
+        <v>35.42229755437894</v>
       </c>
       <c r="N2" t="n">
-        <v>2071.636655635795</v>
+        <v>2058.992815642632</v>
       </c>
       <c r="O2" t="n">
-        <v>45.51523542327113</v>
+        <v>45.37612605371499</v>
       </c>
       <c r="P2" t="n">
-        <v>344.8840018811654</v>
+        <v>344.9594056126742</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -19947,28 +20083,28 @@
         <v>0.0712</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2930425560458905</v>
+        <v>0.2822075941876009</v>
       </c>
       <c r="J3" t="n">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="K3" t="n">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="L3" t="n">
-        <v>0.106123270054326</v>
+        <v>0.09968388227924718</v>
       </c>
       <c r="M3" t="n">
-        <v>5.238176727258246</v>
+        <v>5.270803376098922</v>
       </c>
       <c r="N3" t="n">
-        <v>42.89338208568804</v>
+        <v>43.0235958735465</v>
       </c>
       <c r="O3" t="n">
-        <v>6.54930393902192</v>
+        <v>6.559237446041004</v>
       </c>
       <c r="P3" t="n">
-        <v>347.6507350186717</v>
+        <v>347.7606961996086</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -20025,28 +20161,28 @@
         <v>0.079</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2757088265986481</v>
+        <v>0.2600851327121971</v>
       </c>
       <c r="J4" t="n">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="K4" t="n">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0527478988100577</v>
+        <v>0.04741796081897065</v>
       </c>
       <c r="M4" t="n">
-        <v>7.388224278480021</v>
+        <v>7.424192337881889</v>
       </c>
       <c r="N4" t="n">
-        <v>80.95126664009864</v>
+        <v>81.281142778842</v>
       </c>
       <c r="O4" t="n">
-        <v>8.997292183768327</v>
+        <v>9.015605513710213</v>
       </c>
       <c r="P4" t="n">
-        <v>335.7354075980586</v>
+        <v>335.8939668015076</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -20103,28 +20239,28 @@
         <v>0.0843</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2858022085783356</v>
+        <v>0.2683970630355059</v>
       </c>
       <c r="J5" t="n">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="K5" t="n">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="L5" t="n">
-        <v>0.04406187736311462</v>
+        <v>0.03925091058884744</v>
       </c>
       <c r="M5" t="n">
-        <v>8.434921071649805</v>
+        <v>8.461512280860312</v>
       </c>
       <c r="N5" t="n">
-        <v>105.0896246845879</v>
+        <v>105.4666119289327</v>
       </c>
       <c r="O5" t="n">
-        <v>10.25132306995482</v>
+        <v>10.26969385760514</v>
       </c>
       <c r="P5" t="n">
-        <v>326.7031518414523</v>
+        <v>326.8797962380099</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -20162,7 +20298,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F551"/>
+  <dimension ref="A1:F555"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37765,6 +37901,134 @@
         </is>
       </c>
     </row>
+    <row r="552">
+      <c r="A552" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:17:05+00:00</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>-34.93990911770388,173.57424747333764</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>-34.94026021681358,173.57290098303378</t>
+        </is>
+      </c>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>-34.94103559061494,173.57267068544223</t>
+        </is>
+      </c>
+      <c r="E552" t="inlineStr">
+        <is>
+          <t>-34.94180087015868,173.57267133405534</t>
+        </is>
+      </c>
+      <c r="F552" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:11:06+00:00</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>-34.93987814019953,173.57415875656122</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>-34.940258806612086,173.5728935115156</t>
+        </is>
+      </c>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>-34.94103575133629,173.57266466583812</t>
+        </is>
+      </c>
+      <c r="E553" t="inlineStr">
+        <is>
+          <t>-34.94180200203516,173.5726594773252</t>
+        </is>
+      </c>
+      <c r="F553" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:10:40+00:00</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>-34.939799675295596,173.57393404129425</t>
+        </is>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>-34.94025969302451,173.57289820789845</t>
+        </is>
+      </c>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>-34.94103554385957,173.5726724365998</t>
+        </is>
+      </c>
+      <c r="E554" t="inlineStr">
+        <is>
+          <t>-34.94180165935708,173.57266306697747</t>
+        </is>
+      </c>
+      <c r="F554" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:49+00:00</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>-34.939751061341816,173.57379481683918</t>
+        </is>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>-34.940259632587306,173.57289788769052</t>
+        </is>
+      </c>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>-34.94103557308166,173.5726713421263</t>
+        </is>
+      </c>
+      <c r="E555" t="inlineStr">
+        <is>
+          <t>-34.941802230487156,173.57265708422364</t>
+        </is>
+      </c>
+      <c r="F555" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0032/nzd0032.xlsx
+++ b/data/nzd0032/nzd0032.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F555"/>
+  <dimension ref="A1:F560"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13738,6 +13738,126 @@
         <v>321.16</v>
       </c>
       <c r="F555" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-01 22:10:40+00:00</t>
+        </is>
+      </c>
+      <c r="B556" t="n">
+        <v>393.17</v>
+      </c>
+      <c r="C556" t="n">
+        <v>346.12</v>
+      </c>
+      <c r="D556" t="n">
+        <v>329.83</v>
+      </c>
+      <c r="E556" t="n">
+        <v>320.04</v>
+      </c>
+      <c r="F556" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:16:51+00:00</t>
+        </is>
+      </c>
+      <c r="B557" t="n">
+        <v>379.25</v>
+      </c>
+      <c r="C557" t="n">
+        <v>346.55</v>
+      </c>
+      <c r="D557" t="n">
+        <v>329.24</v>
+      </c>
+      <c r="E557" t="n">
+        <v>318.98</v>
+      </c>
+      <c r="F557" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:30+00:00</t>
+        </is>
+      </c>
+      <c r="B558" t="n">
+        <v>378.79</v>
+      </c>
+      <c r="C558" t="n">
+        <v>347.66</v>
+      </c>
+      <c r="D558" t="n">
+        <v>329.85</v>
+      </c>
+      <c r="E558" t="n">
+        <v>319.28</v>
+      </c>
+      <c r="F558" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-16 22:16:47+00:00</t>
+        </is>
+      </c>
+      <c r="B559" t="n">
+        <v>376.75</v>
+      </c>
+      <c r="C559" t="n">
+        <v>348.53</v>
+      </c>
+      <c r="D559" t="n">
+        <v>330.37</v>
+      </c>
+      <c r="E559" t="n">
+        <v>319.7</v>
+      </c>
+      <c r="F559" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:47+00:00</t>
+        </is>
+      </c>
+      <c r="B560" t="n">
+        <v>375.3</v>
+      </c>
+      <c r="C560" t="n">
+        <v>348.77</v>
+      </c>
+      <c r="D560" t="n">
+        <v>330.19</v>
+      </c>
+      <c r="E560" t="n">
+        <v>319.89</v>
+      </c>
+      <c r="F560" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -13754,7 +13874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B608"/>
+  <dimension ref="A1:B613"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19837,6 +19957,56 @@
       </c>
       <c r="B608" t="n">
         <v>0.09</v>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>2026-06-01 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B609" t="n">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B610" t="n">
+        <v>-0.22</v>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B611" t="n">
+        <v>-0.55</v>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>2026-06-16 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B612" t="n">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B613" t="n">
+        <v>0.88</v>
       </c>
     </row>
   </sheetData>
@@ -20005,28 +20175,28 @@
         <v>0.0793</v>
       </c>
       <c r="I2" t="n">
-        <v>3.161265540541654</v>
+        <v>3.078088584149185</v>
       </c>
       <c r="J2" t="n">
-        <v>554</v>
+        <v>559</v>
       </c>
       <c r="K2" t="n">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2261146599477705</v>
+        <v>0.2184231822061093</v>
       </c>
       <c r="M2" t="n">
-        <v>35.42229755437894</v>
+        <v>35.5148650271741</v>
       </c>
       <c r="N2" t="n">
-        <v>2058.992815642632</v>
+        <v>2062.101417027604</v>
       </c>
       <c r="O2" t="n">
-        <v>45.37612605371499</v>
+        <v>45.41036684533174</v>
       </c>
       <c r="P2" t="n">
-        <v>344.9594056126742</v>
+        <v>345.8069703749194</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -20083,28 +20253,28 @@
         <v>0.0712</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2822075941876009</v>
+        <v>0.2690541205937773</v>
       </c>
       <c r="J3" t="n">
-        <v>554</v>
+        <v>559</v>
       </c>
       <c r="K3" t="n">
-        <v>554</v>
+        <v>559</v>
       </c>
       <c r="L3" t="n">
-        <v>0.09968388227924718</v>
+        <v>0.09200971106568534</v>
       </c>
       <c r="M3" t="n">
-        <v>5.270803376098922</v>
+        <v>5.3088684010933</v>
       </c>
       <c r="N3" t="n">
-        <v>43.0235958735465</v>
+        <v>43.18025933858742</v>
       </c>
       <c r="O3" t="n">
-        <v>6.559237446041004</v>
+        <v>6.571168795472189</v>
       </c>
       <c r="P3" t="n">
-        <v>347.7606961996086</v>
+        <v>347.8947603693396</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -20161,28 +20331,28 @@
         <v>0.079</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2600851327121971</v>
+        <v>0.2382367674499692</v>
       </c>
       <c r="J4" t="n">
-        <v>554</v>
+        <v>559</v>
       </c>
       <c r="K4" t="n">
-        <v>554</v>
+        <v>559</v>
       </c>
       <c r="L4" t="n">
-        <v>0.04741796081897065</v>
+        <v>0.04014671211575471</v>
       </c>
       <c r="M4" t="n">
-        <v>7.424192337881889</v>
+        <v>7.481138052568483</v>
       </c>
       <c r="N4" t="n">
-        <v>81.281142778842</v>
+        <v>82.0220958982357</v>
       </c>
       <c r="O4" t="n">
-        <v>9.015605513710213</v>
+        <v>9.056605097840785</v>
       </c>
       <c r="P4" t="n">
-        <v>335.8939668015076</v>
+        <v>336.1166698016341</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -20239,28 +20409,28 @@
         <v>0.0843</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2683970630355059</v>
+        <v>0.2439806747973242</v>
       </c>
       <c r="J5" t="n">
-        <v>554</v>
+        <v>559</v>
       </c>
       <c r="K5" t="n">
-        <v>554</v>
+        <v>559</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03925091058884744</v>
+        <v>0.03272328813343339</v>
       </c>
       <c r="M5" t="n">
-        <v>8.461512280860312</v>
+        <v>8.50900682348921</v>
       </c>
       <c r="N5" t="n">
-        <v>105.4666119289327</v>
+        <v>106.3562621613543</v>
       </c>
       <c r="O5" t="n">
-        <v>10.26969385760514</v>
+        <v>10.31291724786708</v>
       </c>
       <c r="P5" t="n">
-        <v>326.8797962380099</v>
+        <v>327.1286785594753</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -20298,7 +20468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F555"/>
+  <dimension ref="A1:F560"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38029,6 +38199,166 @@
         </is>
       </c>
     </row>
+    <row r="556">
+      <c r="A556" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-01 22:10:40+00:00</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>-34.93972458937435,173.57371900460464</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>-34.94025659058025,173.57288177055895</t>
+        </is>
+      </c>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>-34.94103617213263,173.57264890542004</t>
+        </is>
+      </c>
+      <c r="E556" t="inlineStr">
+        <is>
+          <t>-34.94180339351474,173.57264490116106</t>
+        </is>
+      </c>
+      <c r="F556" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:16:51+00:00</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>-34.939675587946496,173.57357867144657</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>-34.94025745684738,173.57288636020556</t>
+        </is>
+      </c>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>-34.94103634454164,173.57264244802644</t>
+        </is>
+      </c>
+      <c r="E557" t="inlineStr">
+        <is>
+          <t>-34.941804494236166,173.57263337076216</t>
+        </is>
+      </c>
+      <c r="F557" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:30+00:00</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>-34.939673968643625,173.57357403400306</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>-34.94025969302451,173.57289820789845</t>
+        </is>
+      </c>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>-34.94103616628824,173.57264912431472</t>
+        </is>
+      </c>
+      <c r="E558" t="inlineStr">
+        <is>
+          <t>-34.941804182711344,173.57263663408264</t>
+        </is>
+      </c>
+      <c r="F558" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-16 22:16:47+00:00</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>-34.939666787385306,173.57355346795146</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>-34.940261445703065,173.57290749392843</t>
+        </is>
+      </c>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>-34.94103601433424,173.57265481557684</t>
+        </is>
+      </c>
+      <c r="E559" t="inlineStr">
+        <is>
+          <t>-34.94180374657644,173.57264120273126</t>
+        </is>
+      </c>
+      <c r="F559" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:47+00:00</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>-34.939661683057395,173.57353884992673</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>-34.94026192920048,173.57291005559193</t>
+        </is>
+      </c>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>-34.941036066933734,173.57265284552457</t>
+        </is>
+      </c>
+      <c r="E560" t="inlineStr">
+        <is>
+          <t>-34.941803549277274,173.57264326950084</t>
+        </is>
+      </c>
+      <c r="F560" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
